--- a/corrected-bank-specimens-for-user/01-ecobank/parsed-excel/1778163944552 (acct1) - parsed.xlsx
+++ b/corrected-bank-specimens-for-user/01-ecobank/parsed-excel/1778163944552 (acct1) - parsed.xlsx
@@ -425,7 +425,7 @@
         <v>Exported</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-07-08T16:17:00.820Z</v>
+        <v>2026-07-14T13:50:03.521Z</v>
       </c>
     </row>
     <row r="5">

--- a/corrected-bank-specimens-for-user/01-ecobank/parsed-excel/1778163944552 (acct1) - parsed.xlsx
+++ b/corrected-bank-specimens-for-user/01-ecobank/parsed-excel/1778163944552 (acct1) - parsed.xlsx
@@ -425,7 +425,7 @@
         <v>Exported</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-07-14T13:50:03.521Z</v>
+        <v>2026-07-17T19:29:57.376Z</v>
       </c>
     </row>
     <row r="5">
